--- a/reports/pdf_change_20260910.xlsx
+++ b/reports/pdf_change_20260910.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,482억   ·   현금 15억(0.3%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 6종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,595억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>394</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2651403300</v>
+        <v>2643566640</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-35</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-799312500</v>
+        <v>-796950000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>917966000</v>
+        <v>915252800</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-23</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-817075000</v>
+        <v>-814660000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>953998500</v>
+        <v>951178800</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-21</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-931465500</v>
+        <v>-928712400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>963539500</v>
+        <v>960691600</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-18</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-904365000</v>
+        <v>-901692000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>980490000</v>
+        <v>977592000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-840420000</v>
+        <v>-837936000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2862300000</v>
+        <v>2853840000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-10</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1546860000</v>
+        <v>-1542288000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
         <v>-9</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-824890500</v>
+        <v>-822452400</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>-7</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2202550000</v>
+        <v>-2196040000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,518억   ·   현금 44억(1.2%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,531억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1007,7 +1007,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 35억(1.3%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,613억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1031,7 +1031,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,991억   ·   현금 2억(0.1%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,000억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1164,7 +1164,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 270억   ·   현금 1억(0.5%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1188,7 +1188,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 498억   ·   현금 4억(0.8%)      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 500억      당일 2026-09-10  vs  전영업일 2026-09-09      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
